--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_254_R26.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_254_R26.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.1538</v>
+        <v>8.33</v>
       </c>
       <c r="E2" t="n">
-        <v>7.3765</v>
+        <v>7.6871</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7773</v>
+        <v>0.6429</v>
       </c>
       <c r="G2" t="n">
         <v>5.4064</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4252</v>
+        <v>0.6014</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0395</v>
+        <v>0.3501</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3857</v>
+        <v>0.2513</v>
       </c>
       <c r="V2" t="n">
         <v>0.9304</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6995</v>
+        <v>4.6674</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0119</v>
+        <v>4.5844</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3125</v>
+        <v>0.083</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0767</v>
+        <v>-0.0229</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3095</v>
+        <v>-0.9195</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7672</v>
+        <v>0.8966</v>
       </c>
       <c r="J3" t="n">
-        <v>5.6603</v>
+        <v>1.2143</v>
       </c>
       <c r="K3" t="n">
-        <v>1.943</v>
+        <v>-0.1072</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7173</v>
+        <v>1.3215</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5837</v>
+        <v>-1.2372</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6335</v>
+        <v>-0.8123</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.4248</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1589</v>
+        <v>0.6181</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9752</v>
+        <v>0.1535</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1836</v>
+        <v>0.4646</v>
       </c>
       <c r="V3" t="n">
+        <v>2.6805</v>
+      </c>
+      <c r="W3" t="n">
+        <v>3.2166</v>
+      </c>
+      <c r="X3" t="n">
         <v>-0.5361</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8679</v>
+        <v>3.9827</v>
       </c>
       <c r="E4" t="n">
-        <v>3.6841</v>
+        <v>5.4968</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1838</v>
+        <v>-1.5141</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0229</v>
+        <v>4.0767</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9195</v>
+        <v>1.3095</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8966</v>
+        <v>2.7672</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2143</v>
+        <v>5.6603</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1072</v>
+        <v>1.943</v>
       </c>
       <c r="L4" t="n">
-        <v>1.3215</v>
+        <v>3.7173</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2372</v>
+        <v>-1.5837</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8123</v>
+        <v>-0.6335</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4248</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1814</v>
+        <v>0.4422</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7468</v>
+        <v>0.4602</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5654</v>
+        <v>-0.018</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6805</v>
+        <v>-0.5361</v>
       </c>
       <c r="W4" t="n">
-        <v>3.2166</v>
+        <v>0.5361</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1845</v>
+        <v>3.1405</v>
       </c>
       <c r="E5" t="n">
-        <v>4.71</v>
+        <v>4.4309</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5256</v>
+        <v>-1.2903</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0195</v>
@@ -844,13 +844,13 @@
         <v>1.6237</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1138</v>
+        <v>0.0698</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8259</v>
+        <v>0.5467</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7121</v>
+        <v>-0.4769</v>
       </c>
       <c r="V5" t="n">
         <v>1.4665</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.7252</v>
+        <v>2.6141</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8318</v>
+        <v>1.5527</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8934</v>
+        <v>1.0614</v>
       </c>
       <c r="G6" t="n">
         <v>3.7937</v>
@@ -922,13 +922,13 @@
         <v>1.3917</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0532</v>
+        <v>-0.1643</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6018</v>
+        <v>0.3227</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.655</v>
+        <v>-0.487</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>D. FLACCADORI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5093</v>
+        <v>1.7966</v>
       </c>
       <c r="E7" t="n">
-        <v>1.8156</v>
+        <v>2.2086</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3062</v>
+        <v>-0.412</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4061</v>
+        <v>2.8042</v>
       </c>
       <c r="H7" t="n">
-        <v>0.526</v>
+        <v>2.0613</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8801</v>
+        <v>0.7429</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4026</v>
+        <v>2.6862</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1512</v>
+        <v>1.3612</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2514</v>
+        <v>1.325</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0035</v>
+        <v>0.118</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3748</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3713</v>
+        <v>-0.5821</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3607</v>
+        <v>-0.8995</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4129</v>
+        <v>-0.1375</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7736</v>
+        <v>-0.762</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FLACCADORI</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.2582</v>
+        <v>1.1219</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9727</v>
+        <v>1.4617</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7145</v>
+        <v>-0.3398</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8042</v>
+        <v>1.4061</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0613</v>
+        <v>0.526</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7429</v>
+        <v>0.8801</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6862</v>
+        <v>1.4026</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3612</v>
+        <v>0.1512</v>
       </c>
       <c r="L8" t="n">
-        <v>1.325</v>
+        <v>1.2514</v>
       </c>
       <c r="M8" t="n">
-        <v>0.118</v>
+        <v>0.0035</v>
       </c>
       <c r="N8" t="n">
-        <v>0.7000999999999999</v>
+        <v>0.3748</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5821</v>
+        <v>-0.3713</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.4378</v>
+        <v>-0.7481</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>0.0591</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0644</v>
+        <v>-0.8072</v>
       </c>
       <c r="V8" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5854</v>
+        <v>-0.6697</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3991</v>
+        <v>0.2812</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9845</v>
+        <v>-0.9509</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7571</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5241</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>0.1456</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7877</v>
+        <v>-0.7541</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1822</v>
+        <v>-1.1308</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4622</v>
+        <v>-0.1083</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.72</v>
+        <v>-1.0224</v>
       </c>
       <c r="G10" t="n">
         <v>-0.848</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6383</v>
+        <v>-0.5869</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3396</v>
+        <v>-0.642</v>
       </c>
       <c r="V10" t="n">
         <v>0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.3809</v>
+        <v>-1.2294</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1505</v>
+        <v>1.2684</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5314</v>
+        <v>-2.4978</v>
       </c>
       <c r="G11" t="n">
         <v>1.8497</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2333</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0092</v>
+        <v>0.0244</v>
       </c>
       <c r="V11" t="n">
         <v>-0.6778999999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>22.2499</v>
+        <v>22.6233</v>
       </c>
       <c r="E12" t="n">
-        <v>28.49</v>
+        <v>28.8635</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.2402</v>
+        <v>-6.24</v>
       </c>
       <c r="G12" t="n">
         <v>17.6893</v>
@@ -1390,16 +1390,16 @@
         <v>9.2782</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.7309</v>
+        <v>-1.3574</v>
       </c>
       <c r="T12" t="n">
-        <v>1.476</v>
+        <v>1.8494</v>
       </c>
       <c r="U12" t="n">
         <v>-3.2069</v>
       </c>
       <c r="V12" t="n">
-        <v>6.291400000000001</v>
+        <v>6.291399999999999</v>
       </c>
       <c r="W12" t="n">
         <v>10.0752</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2253</v>
+        <v>4.9215</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7561</v>
+        <v>7.2843</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.5308</v>
+        <v>-2.3628</v>
       </c>
       <c r="G13" t="n">
         <v>4.3011</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6743</v>
+        <v>0.3705</v>
       </c>
       <c r="T13" t="n">
-        <v>1.0578</v>
+        <v>0.586</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3835</v>
+        <v>-0.2155</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6778999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7459</v>
+        <v>0.6951000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3309</v>
+        <v>1.213</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5851</v>
+        <v>-0.5178</v>
       </c>
       <c r="G14" t="n">
         <v>0.9043</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>0.4498</v>
+        <v>0.3991</v>
       </c>
       <c r="T14" t="n">
-        <v>0.7196</v>
+        <v>0.6016</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0888</v>
+        <v>-0.156</v>
       </c>
       <c r="E15" t="n">
         <v>2.4245</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.5133</v>
+        <v>-2.5805</v>
       </c>
       <c r="G15" t="n">
         <v>0.4922</v>
@@ -1624,13 +1624,13 @@
         <v>0.9278</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1871</v>
+        <v>0.1199</v>
       </c>
       <c r="T15" t="n">
         <v>0.3541</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1669</v>
+        <v>-0.2341</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1124</v>
+        <v>-0.7428</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8677</v>
+        <v>-0.2615</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9801</v>
+        <v>-0.4813</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.1712</v>
+        <v>-1.0033</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9516</v>
+        <v>-0.8127</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.1228</v>
+        <v>-0.1907</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8997000000000001</v>
+        <v>0.4302</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6537</v>
+        <v>-0.3795</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.754</v>
+        <v>0.8097</v>
       </c>
       <c r="M16" t="n">
-        <v>-4.0709</v>
+        <v>-1.4335</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7021</v>
+        <v>-0.4331</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.3688</v>
+        <v>-1.0004</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
         <v>0.9278</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8474</v>
+        <v>0.4925</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6844</v>
+        <v>0.4681</v>
       </c>
       <c r="U16" t="n">
-        <v>0.163</v>
+        <v>0.0244</v>
       </c>
       <c r="V16" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4677</v>
+        <v>-1.0463</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0872</v>
+        <v>3.4545</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3805</v>
+        <v>-4.5008</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0033</v>
+        <v>-1.6912</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.8127</v>
+        <v>0.1056</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1907</v>
+        <v>-1.7968</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4302</v>
+        <v>1.4788</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3795</v>
+        <v>0.696</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8097</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4335</v>
+        <v>-3.17</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4331</v>
+        <v>-0.5904</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0004</v>
+        <v>-2.5796</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2324</v>
+        <v>-0.5149</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3576</v>
+        <v>-0.1687</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1252</v>
+        <v>-0.3462</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,40 +1813,40 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.996</v>
+        <v>-1.8702</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5632</v>
+        <v>1.2779</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.5592</v>
+        <v>-3.1481</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2481</v>
+        <v>-3.1712</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9135</v>
+        <v>1.9516</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3345</v>
+        <v>-5.1228</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0569</v>
+        <v>0.8997000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.8298</v>
+        <v>3.6537</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7729</v>
+        <v>-2.754</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1912</v>
+        <v>-4.0709</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0838</v>
+        <v>-1.7021</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1074</v>
+        <v>-2.3688</v>
       </c>
       <c r="P18" t="n">
         <v>0.9278</v>
@@ -1858,28 +1858,28 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6105</v>
+        <v>0.0896</v>
       </c>
       <c r="T18" t="n">
-        <v>1.6201</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0097</v>
+        <v>-0.005</v>
       </c>
       <c r="V18" t="n">
-        <v>-2.2862</v>
+        <v>0.2836</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X18" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1244</v>
+        <v>-2.6529</v>
       </c>
       <c r="E19" t="n">
-        <v>2.5109</v>
+        <v>0.9735</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.6352</v>
+        <v>-3.6264</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6912</v>
+        <v>-2.2481</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1056</v>
+        <v>-1.9135</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7968</v>
+        <v>-0.3345</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4788</v>
+        <v>-0.0569</v>
       </c>
       <c r="K19" t="n">
-        <v>0.696</v>
+        <v>-0.8298</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.7729</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.17</v>
+        <v>-2.1912</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5904</v>
+        <v>-1.0838</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.5796</v>
+        <v>-1.1074</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5929</v>
+        <v>0.9535</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1123</v>
+        <v>1.0304</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4806</v>
+        <v>-0.0769</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1444</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1444</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. SPAGNOLO</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8055</v>
+        <v>-4.8842</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6557</v>
+        <v>-2.5925</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1498</v>
+        <v>-2.2917</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.5362</v>
+        <v>-2.6322</v>
       </c>
       <c r="H20" t="n">
-        <v>-3.575</v>
+        <v>-0.9458</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.9612</v>
+        <v>-1.6864</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.9379</v>
+        <v>-0.0766</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.0277</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9102</v>
+        <v>-0.1607</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5983</v>
+        <v>-2.5556</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5473</v>
+        <v>-1.0299</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.051</v>
+        <v>-1.5257</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8931</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1404</v>
+        <v>-0.1964</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2473</v>
+        <v>0.1041</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>E. OMORUYI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0529</v>
+        <v>-5.0135</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8284</v>
+        <v>-0.0999</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2245</v>
+        <v>-4.9137</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6322</v>
+        <v>-3.4171</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9458</v>
+        <v>-0.0745</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6864</v>
+        <v>-3.3426</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0766</v>
+        <v>-0.0504</v>
       </c>
       <c r="K21" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.6624</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1607</v>
+        <v>-0.7127</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5556</v>
+        <v>-3.3667</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0299</v>
+        <v>-0.7369</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5257</v>
+        <v>-2.6299</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2609</v>
+        <v>-0.6840000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4323</v>
+        <v>-0.5856</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1713</v>
+        <v>-0.0984</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. OMORUYI</t>
+          <t>M. SPAGNOLO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2494</v>
+        <v>-5.2945</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3358</v>
+        <v>-3.2455</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9137</v>
+        <v>-2.049</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4171</v>
+        <v>-6.5362</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0745</v>
+        <v>-3.575</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.3426</v>
+        <v>-2.9612</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.0504</v>
+        <v>-3.9379</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6624</v>
+        <v>-3.0277</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7127</v>
+        <v>-0.9102</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.3667</v>
+        <v>-2.5983</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7369</v>
+        <v>-0.5473</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.6299</v>
+        <v>-2.051</v>
       </c>
       <c r="P22" t="n">
         <v>0.6959</v>
@@ -2170,22 +2170,22 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.9199000000000001</v>
+        <v>0.4042</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8215</v>
+        <v>0.5507</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0984</v>
+        <v>-0.1465</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6083</v>
+        <v>0.1418</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.324</v>
+        <v>-6.2061</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3062</v>
+        <v>-4.1883</v>
       </c>
       <c r="F23" t="n">
         <v>-2.0178</v>
@@ -2248,10 +2248,10 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0747</v>
+        <v>0.1926</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3541</v>
+        <v>0.472</v>
       </c>
       <c r="U23" t="n">
         <v>-0.2794</v>
@@ -2284,16 +2284,16 @@
         <v>-22.2499</v>
       </c>
       <c r="E24" t="n">
-        <v>6.239999999999999</v>
+        <v>6.24</v>
       </c>
       <c r="F24" t="n">
-        <v>-28.49</v>
+        <v>-28.4899</v>
       </c>
       <c r="G24" t="n">
         <v>-17.6892</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.556200000000001</v>
+        <v>-4.5562</v>
       </c>
       <c r="I24" t="n">
         <v>-13.1329</v>
@@ -2302,7 +2302,7 @@
         <v>8.5276</v>
       </c>
       <c r="K24" t="n">
-        <v>3.760700000000001</v>
+        <v>3.760699999999999</v>
       </c>
       <c r="L24" t="n">
         <v>4.767</v>
@@ -2317,7 +2317,7 @@
         <v>-17.8999</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
         <v>-9.2781</v>
@@ -2326,10 +2326,10 @@
         <v>9.2782</v>
       </c>
       <c r="S24" t="n">
-        <v>1.7308</v>
+        <v>1.7307</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2068</v>
+        <v>3.2069</v>
       </c>
       <c r="U24" t="n">
         <v>-1.476</v>
